--- a/data/2604 멀티캠퍼스_매출정산_변환2.xlsx
+++ b/data/2604 멀티캠퍼스_매출정산_변환2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minion\Desktop\알라딘\알라딘아카데미 정산관련\26.04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C5913C-E00B-4AAC-A432-52B9990A40C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563297C-66EE-4F72-BDB2-0863F6982517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29100" yWindow="2430" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26775" yWindow="1305" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 입력" sheetId="1" r:id="rId1"/>
@@ -234,28 +234,6 @@
   </si>
   <si>
     <t>샘호트만</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김광석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>김학균,안승찬</t>
@@ -291,6 +269,10 @@
       </rPr>
       <t>안승찬</t>
     </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>김광석</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -471,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,6 +519,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -547,13 +538,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1158,8 +1143,8 @@
       <c r="C9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>66</v>
+      <c r="D9" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>53</v>
@@ -1192,8 +1177,8 @@
       <c r="C10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>66</v>
+      <c r="D10" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>53</v>
@@ -1226,8 +1211,8 @@
       <c r="C11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>66</v>
+      <c r="D11" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>53</v>
@@ -1260,8 +1245,8 @@
       <c r="C12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>66</v>
+      <c r="D12" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>53</v>
@@ -1294,8 +1279,8 @@
       <c r="C13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>66</v>
+      <c r="D13" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>53</v>
@@ -1328,8 +1313,8 @@
       <c r="C14" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>67</v>
+      <c r="D14" s="25" t="s">
+        <v>66</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>53</v>
@@ -1362,8 +1347,8 @@
       <c r="C15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>68</v>
+      <c r="D15" s="23" t="s">
+        <v>67</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>53</v>
@@ -1396,8 +1381,8 @@
       <c r="C16" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>68</v>
+      <c r="D16" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>53</v>
@@ -4908,28 +4893,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="2:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="4" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="5" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
